--- a/Proyecto Interno/review-food-security-paper/07_tables/final/tab04_afford_annual.xlsx
+++ b/Proyecto Interno/review-food-security-paper/07_tables/final/tab04_afford_annual.xlsx
@@ -41,7 +41,7 @@
     <t xml:space="preserve">5.0 (4.2)</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8 (6.3)</t>
+    <t xml:space="preserve">13.1 (6.3)</t>
   </si>
   <si>
     <t xml:space="preserve">27.4 (8.2)</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.9 (1.1)</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6 (1.2)</t>
+    <t xml:space="preserve">7.7 (1.2)</t>
   </si>
   <si>
     <t xml:space="preserve">18.9 (3.1)</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">10.7 (7.7)</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4 (10.9)</t>
+    <t xml:space="preserve">20.6 (10.9)</t>
   </si>
   <si>
     <t xml:space="preserve">35.6 (13.0)</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">5.2 (1.4)</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2 (1.9)</t>
+    <t xml:space="preserve">15.4 (2.0)</t>
   </si>
   <si>
     <t xml:space="preserve">31.9 (2.5)</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">4.7 (1.1)</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8 (1.3)</t>
+    <t xml:space="preserve">14.1 (1.3)</t>
   </si>
   <si>
     <t xml:space="preserve">29.2 (2.1)</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">3.8 (1.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7 (1.9)</t>
+    <t xml:space="preserve">12.4 (2.0)</t>
   </si>
   <si>
     <t xml:space="preserve">28.2 (3.1)</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">2.4 (0.6)</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3 (1.6)</t>
+    <t xml:space="preserve">8.7 (1.6)</t>
   </si>
   <si>
     <t xml:space="preserve">20.8 (3.1)</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">4.4 (2.8)</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5 (5.2)</t>
+    <t xml:space="preserve">13.8 (5.2)</t>
   </si>
   <si>
     <t xml:space="preserve">26.0 (6.9)</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">3.3 (0.6)</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4 (1.4)</t>
+    <t xml:space="preserve">9.5 (1.4)</t>
   </si>
   <si>
     <t xml:space="preserve">19.0 (2.5)</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">8.0 (5.1)</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0 (9.0)</t>
+    <t xml:space="preserve">19.2 (9.0)</t>
   </si>
   <si>
     <t xml:space="preserve">31.1 (11.8)</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">4.1 (0.8)</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3 (1.6)</t>
+    <t xml:space="preserve">13.5 (1.6)</t>
   </si>
   <si>
     <t xml:space="preserve">26.5 (2.1)</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">4.2 (0.7)</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9 (1.7)</t>
+    <t xml:space="preserve">14.3 (1.7)</t>
   </si>
   <si>
     <t xml:space="preserve">28.9 (2.2)</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">4.6 (1.4)</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0 (3.9)</t>
+    <t xml:space="preserve">15.6 (4.3)</t>
   </si>
   <si>
     <t xml:space="preserve">28.5 (4.4)</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">2.5 (1.0)</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6 (2.1)</t>
+    <t xml:space="preserve">11.0 (2.3)</t>
   </si>
   <si>
     <t xml:space="preserve">22.1 (4.0)</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">6.3 (4.4)</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3 (7.3)</t>
+    <t xml:space="preserve">19.6 (7.3)</t>
   </si>
   <si>
     <t xml:space="preserve">35.0 (8.3)</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">11.9 (8.5)</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6 (11.9)</t>
+    <t xml:space="preserve">25.4 (12.0)</t>
   </si>
   <si>
     <t xml:space="preserve">41.4 (13.0)</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">6.1 (1.7)</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2 (4.5)</t>
+    <t xml:space="preserve">18.3 (4.5)</t>
   </si>
   <si>
     <t xml:space="preserve">34.7 (4.5)</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">4.9 (1.2)</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6 (3.1)</t>
+    <t xml:space="preserve">18.1 (3.2)</t>
   </si>
   <si>
     <t xml:space="preserve">34.2 (2.3)</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">6.0 (1.4)</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6 (2.7)</t>
+    <t xml:space="preserve">24.1 (2.6)</t>
   </si>
   <si>
     <t xml:space="preserve">39.4 (3.2)</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">4.7 (1.4)</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0 (3.6)</t>
+    <t xml:space="preserve">20.7 (3.8)</t>
   </si>
   <si>
     <t xml:space="preserve">37.0 (3.1)</t>
